--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114940074</v>
+        <v>121667734</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>6649106</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -775,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114939996</v>
+        <v>121667654</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>6649066</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114940113</v>
+        <v>121667773</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>6649000</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -989,17 +989,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114940112</v>
+        <v>121667772</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>6649026</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114939995</v>
+        <v>121667653</v>
       </c>
       <c r="B6" t="n">
-        <v>90532</v>
+        <v>90929</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>6649004</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114940115</v>
+        <v>121667775</v>
       </c>
       <c r="B7" t="n">
-        <v>99909</v>
+        <v>100376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>6649114</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114940075</v>
+        <v>121667735</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>90942</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>6649140</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1417,17 +1417,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114940114</v>
+        <v>121667774</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>6649047</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1524,21 +1524,21 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114940073</v>
+        <v>121667732</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1577,7 +1577,7 @@
         <v>6649044</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667734</v>
       </c>
       <c r="B2" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121667654</v>
       </c>
       <c r="B3" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>121667773</v>
       </c>
       <c r="B4" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>121667772</v>
       </c>
       <c r="B5" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>121667653</v>
       </c>
       <c r="B6" t="n">
-        <v>90929</v>
+        <v>90932</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>121667775</v>
       </c>
       <c r="B7" t="n">
-        <v>100376</v>
+        <v>100379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>121667735</v>
       </c>
       <c r="B8" t="n">
-        <v>90942</v>
+        <v>90945</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>121667774</v>
       </c>
       <c r="B9" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
+          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
+          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
+          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
+          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667734</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>121667654</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>121667773</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>121667772</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>121667653</v>
       </c>
       <c r="B6" t="n">
-        <v>90932</v>
+        <v>90946</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
         <v>121667775</v>
       </c>
       <c r="B7" t="n">
-        <v>100379</v>
+        <v>100397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>121667735</v>
       </c>
       <c r="B8" t="n">
-        <v>90945</v>
+        <v>90959</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         <v>121667774</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>121667732</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667734</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121667654</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
+          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>121667773</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>121667772</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>121667653</v>
       </c>
       <c r="B6" t="n">
-        <v>90946</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
+          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
         <v>121667775</v>
       </c>
       <c r="B7" t="n">
-        <v>100397</v>
+        <v>100399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>121667735</v>
       </c>
       <c r="B8" t="n">
-        <v>90959</v>
+        <v>90961</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>121667774</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667734</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121667654</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>121667773</v>
       </c>
       <c r="B4" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>121667772</v>
       </c>
       <c r="B5" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>121667653</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>90949</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Enviro Planning, Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Anders Esplund, Enviro Planning, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
         <v>121667775</v>
       </c>
       <c r="B7" t="n">
-        <v>100399</v>
+        <v>100406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>121667735</v>
       </c>
       <c r="B8" t="n">
-        <v>90961</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>121667774</v>
       </c>
       <c r="B9" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -1534,11 +1534,11 @@
         <v>121667732</v>
       </c>
       <c r="B10" t="n">
-        <v>57381</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>121667732</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>121667732</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>121667732</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 54719-2023 artfynd.xlsx
+++ b/artfynd/A 54719-2023 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>121667732</v>
       </c>
       <c r="B10" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
